--- a/excels/1급_분개문제(AI).xlsx
+++ b/excels/1급_분개문제(AI).xlsx
@@ -1,21 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-19T12:59:01Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-20T06:42:03Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -125,7 +124,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -408,7 +407,23 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8444,7 +8459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8517,7 +8532,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -8741,7 +8756,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -8823,7 +8838,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -9035,7 +9050,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -9091,7 +9106,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -9147,7 +9162,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -9233,7 +9248,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -9319,7 +9334,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -9655,7 +9670,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -9815,7 +9830,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -10005,7 +10020,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -10083,7 +10098,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -10113,7 +10128,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -10165,7 +10180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -10403,7 +10418,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -10885,7 +10900,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -10993,7 +11008,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -11161,7 +11176,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11351,7 +11366,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -11429,7 +11444,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -11571,7 +11586,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -11687,7 +11702,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -11739,7 +11754,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -12201,7 +12216,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -12339,7 +12354,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -12555,7 +12570,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -12581,7 +12596,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -12611,7 +12626,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -12727,7 +12742,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -12899,7 +12914,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -12989,7 +13004,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -13019,7 +13034,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -13179,7 +13194,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -13269,7 +13284,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -13377,7 +13392,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -13787,7 +13802,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -13951,7 +13966,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -13981,7 +13996,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -14007,7 +14022,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -14089,7 +14104,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -14149,7 +14164,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -14369,7 +14384,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -14395,7 +14410,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -14421,7 +14436,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -14473,7 +14488,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -14503,7 +14518,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -14589,7 +14604,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -14641,7 +14656,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -14723,7 +14738,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -14943,7 +14958,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -14969,7 +14984,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -15103,7 +15118,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -15159,7 +15174,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -15487,7 +15502,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -15777,7 +15792,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -15833,7 +15848,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -15993,7 +16008,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -16213,7 +16228,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -16325,7 +16340,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -16433,7 +16448,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -16489,7 +16504,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -16515,7 +16530,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -16627,7 +16642,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -16713,7 +16728,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -16955,7 +16970,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -17011,7 +17026,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -17037,7 +17052,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -17089,7 +17104,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -17487,7 +17502,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -18053,7 +18068,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -18131,7 +18146,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -18187,7 +18202,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -18243,7 +18258,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -18347,7 +18362,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(제)</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -18671,7 +18686,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -18701,7 +18716,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -18783,7 +18798,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -18865,7 +18880,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -18895,7 +18910,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -19059,7 +19074,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C388" t="n">
